--- a/Team-Data/2008-09/12-18-2008-09.xlsx
+++ b/Team-Data/2008-09/12-18-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE2" t="n">
         <v>9</v>
@@ -748,7 +815,7 @@
         <v>10</v>
       </c>
       <c r="AG2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
         <v>24</v>
@@ -775,10 +842,10 @@
         <v>24</v>
       </c>
       <c r="AP2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR2" t="n">
         <v>20</v>
@@ -802,7 +869,7 @@
         <v>11</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ2" t="n">
         <v>6</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -843,85 +910,85 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.92</v>
+        <v>0.923</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J3" t="n">
         <v>75.7</v>
       </c>
       <c r="K3" t="n">
-        <v>0.476</v>
+        <v>0.475</v>
       </c>
       <c r="L3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M3" t="n">
         <v>15.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.361</v>
+        <v>0.356</v>
       </c>
       <c r="O3" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="P3" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.766</v>
+        <v>0.76</v>
       </c>
       <c r="R3" t="n">
         <v>10.8</v>
       </c>
       <c r="S3" t="n">
-        <v>33</v>
+        <v>32.8</v>
       </c>
       <c r="T3" t="n">
-        <v>43.9</v>
+        <v>43.6</v>
       </c>
       <c r="U3" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="V3" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="W3" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X3" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="AA3" t="n">
         <v>24.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.7</v>
+        <v>100.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -933,10 +1000,10 @@
         <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ3" t="n">
         <v>29</v>
@@ -945,34 +1012,34 @@
         <v>4</v>
       </c>
       <c r="AL3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM3" t="n">
         <v>22</v>
       </c>
       <c r="AN3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO3" t="n">
         <v>2</v>
       </c>
       <c r="AP3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AR3" t="n">
         <v>19</v>
       </c>
       <c r="AS3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AT3" t="n">
         <v>6</v>
       </c>
       <c r="AU3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV3" t="n">
         <v>28</v>
@@ -981,7 +1048,7 @@
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
@@ -993,10 +1060,10 @@
         <v>2</v>
       </c>
       <c r="BB3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE4" t="n">
         <v>24</v>
@@ -1115,13 +1182,13 @@
         <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
       </c>
       <c r="AJ4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK4" t="n">
         <v>29</v>
@@ -1136,13 +1203,13 @@
         <v>17</v>
       </c>
       <c r="AO4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AP4" t="n">
         <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR4" t="n">
         <v>21</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -1207,88 +1274,88 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
         <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>0.458</v>
+        <v>0.48</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J5" t="n">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.439</v>
+        <v>0.441</v>
       </c>
       <c r="L5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="M5" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.369</v>
+        <v>0.371</v>
       </c>
       <c r="O5" t="n">
-        <v>19.1</v>
+        <v>19.7</v>
       </c>
       <c r="P5" t="n">
-        <v>23.7</v>
+        <v>24.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.803</v>
       </c>
       <c r="R5" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S5" t="n">
-        <v>31.2</v>
+        <v>31</v>
       </c>
       <c r="T5" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
       <c r="U5" t="n">
-        <v>19.9</v>
+        <v>20.2</v>
       </c>
       <c r="V5" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W5" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X5" t="n">
         <v>5.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.1</v>
+        <v>20.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.5</v>
+        <v>-1.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="AE5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AF5" t="n">
         <v>17</v>
@@ -1297,16 +1364,16 @@
         <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL5" t="n">
         <v>17</v>
@@ -1318,25 +1385,25 @@
         <v>10</v>
       </c>
       <c r="AO5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP5" t="n">
         <v>14</v>
       </c>
-      <c r="AP5" t="n">
-        <v>20</v>
-      </c>
       <c r="AQ5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR5" t="n">
         <v>11</v>
       </c>
       <c r="AS5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV5" t="n">
         <v>20</v>
@@ -1348,19 +1415,19 @@
         <v>8</v>
       </c>
       <c r="AY5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -1389,94 +1456,94 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="n">
         <v>21</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.875</v>
+        <v>0.84</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>38.4</v>
+        <v>38</v>
       </c>
       <c r="J6" t="n">
-        <v>79.90000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.48</v>
+        <v>0.479</v>
       </c>
       <c r="L6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="M6" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0.337</v>
+        <v>0.333</v>
       </c>
       <c r="O6" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="P6" t="n">
-        <v>25</v>
+        <v>25.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.781</v>
+        <v>0.778</v>
       </c>
       <c r="R6" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="S6" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T6" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U6" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="V6" t="n">
-        <v>12.4</v>
+        <v>12.8</v>
       </c>
       <c r="W6" t="n">
         <v>7.9</v>
       </c>
       <c r="X6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.7</v>
+        <v>21</v>
       </c>
       <c r="AB6" t="n">
-        <v>103</v>
+        <v>102.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>13.9</v>
+        <v>13.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH6" t="n">
         <v>24</v>
@@ -1485,13 +1552,13 @@
         <v>5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK6" t="n">
         <v>2</v>
       </c>
       <c r="AL6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AM6" t="n">
         <v>8</v>
@@ -1500,28 +1567,28 @@
         <v>24</v>
       </c>
       <c r="AO6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP6" t="n">
         <v>11</v>
       </c>
-      <c r="AP6" t="n">
-        <v>12</v>
-      </c>
       <c r="AQ6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT6" t="n">
         <v>11</v>
       </c>
       <c r="AU6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW6" t="n">
         <v>8</v>
@@ -1533,10 +1600,10 @@
         <v>2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BB6" t="n">
         <v>6</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE7" t="n">
         <v>13</v>
@@ -1658,13 +1725,13 @@
         <v>10</v>
       </c>
       <c r="AG7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH7" t="n">
         <v>3</v>
       </c>
       <c r="AI7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AJ7" t="n">
         <v>7</v>
@@ -1673,7 +1740,7 @@
         <v>14</v>
       </c>
       <c r="AL7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM7" t="n">
         <v>9</v>
@@ -1709,7 +1776,7 @@
         <v>19</v>
       </c>
       <c r="AX7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY7" t="n">
         <v>14</v>
@@ -1721,10 +1788,10 @@
         <v>25</v>
       </c>
       <c r="BB7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>5.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1846,10 +1913,10 @@
         <v>17</v>
       </c>
       <c r="AI8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
@@ -1861,7 +1928,7 @@
         <v>16</v>
       </c>
       <c r="AN8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR8" t="n">
         <v>22</v>
@@ -1894,7 +1961,7 @@
         <v>4</v>
       </c>
       <c r="AY8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ8" t="n">
         <v>20</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>0.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE9" t="n">
         <v>13</v>
@@ -2022,7 +2089,7 @@
         <v>7</v>
       </c>
       <c r="AG9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH9" t="n">
         <v>24</v>
@@ -2034,7 +2101,7 @@
         <v>23</v>
       </c>
       <c r="AK9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL9" t="n">
         <v>20</v>
@@ -2046,13 +2113,13 @@
         <v>6</v>
       </c>
       <c r="AO9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>19</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>18</v>
       </c>
       <c r="AR9" t="n">
         <v>24</v>
@@ -2067,7 +2134,7 @@
         <v>8</v>
       </c>
       <c r="AV9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW9" t="n">
         <v>20</v>
@@ -2076,7 +2143,7 @@
         <v>13</v>
       </c>
       <c r="AY9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ9" t="n">
         <v>17</v>
@@ -2088,7 +2155,7 @@
         <v>24</v>
       </c>
       <c r="BC9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-5.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
         <v>25</v>
@@ -2207,7 +2274,7 @@
         <v>26</v>
       </c>
       <c r="AH10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2219,7 +2286,7 @@
         <v>19</v>
       </c>
       <c r="AL10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM10" t="n">
         <v>15</v>
@@ -2231,7 +2298,7 @@
         <v>3</v>
       </c>
       <c r="AP10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ10" t="n">
         <v>21</v>
@@ -2246,7 +2313,7 @@
         <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV10" t="n">
         <v>17</v>
@@ -2261,7 +2328,7 @@
         <v>25</v>
       </c>
       <c r="AZ10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA10" t="n">
         <v>1</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -2377,16 +2444,16 @@
         <v>3.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF11" t="n">
         <v>7</v>
       </c>
       <c r="AG11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH11" t="n">
         <v>17</v>
@@ -2395,13 +2462,13 @@
         <v>29</v>
       </c>
       <c r="AJ11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM11" t="n">
         <v>12</v>
@@ -2413,7 +2480,7 @@
         <v>6</v>
       </c>
       <c r="AP11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ11" t="n">
         <v>2</v>
@@ -2425,7 +2492,7 @@
         <v>5</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AU11" t="n">
         <v>24</v>
@@ -2434,7 +2501,7 @@
         <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX11" t="n">
         <v>28</v>
@@ -2443,7 +2510,7 @@
         <v>28</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA11" t="n">
         <v>13</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -2559,19 +2626,19 @@
         <v>-2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE12" t="n">
         <v>22</v>
       </c>
       <c r="AF12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG12" t="n">
         <v>22</v>
       </c>
       <c r="AH12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI12" t="n">
         <v>3</v>
@@ -2589,7 +2656,7 @@
         <v>10</v>
       </c>
       <c r="AN12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO12" t="n">
         <v>23</v>
@@ -2604,7 +2671,7 @@
         <v>7</v>
       </c>
       <c r="AS12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT12" t="n">
         <v>3</v>
@@ -2634,7 +2701,7 @@
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-4.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2753,13 +2820,13 @@
         <v>25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK13" t="n">
         <v>28</v>
@@ -2810,7 +2877,7 @@
         <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB13" t="n">
         <v>26</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F14" t="n">
         <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>0.87</v>
+        <v>0.875</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="J14" t="n">
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="K14" t="n">
         <v>0.473</v>
@@ -2872,37 +2939,37 @@
         <v>6.7</v>
       </c>
       <c r="M14" t="n">
-        <v>18.3</v>
+        <v>18</v>
       </c>
       <c r="N14" t="n">
-        <v>0.366</v>
+        <v>0.374</v>
       </c>
       <c r="O14" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="P14" t="n">
-        <v>28.4</v>
+        <v>28</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.758</v>
+        <v>0.76</v>
       </c>
       <c r="R14" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="S14" t="n">
-        <v>33</v>
+        <v>33.3</v>
       </c>
       <c r="T14" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="U14" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="V14" t="n">
         <v>14.2</v>
       </c>
       <c r="W14" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="X14" t="n">
         <v>5.7</v>
@@ -2911,28 +2978,28 @@
         <v>4.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA14" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="AD14" t="n">
         <v>23</v>
       </c>
-      <c r="AB14" t="n">
-        <v>108.9</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>27</v>
-      </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="n">
         <v>24</v>
@@ -2947,13 +3014,13 @@
         <v>5</v>
       </c>
       <c r="AL14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AM14" t="n">
         <v>14</v>
       </c>
-      <c r="AM14" t="n">
-        <v>13</v>
-      </c>
       <c r="AN14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
@@ -2962,13 +3029,13 @@
         <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AR14" t="n">
         <v>5</v>
       </c>
       <c r="AS14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2977,28 +3044,28 @@
         <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
       </c>
       <c r="AX14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY14" t="n">
         <v>5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
       </c>
       <c r="BC14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -3105,13 +3172,13 @@
         <v>-3.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE15" t="n">
         <v>22</v>
       </c>
       <c r="AF15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG15" t="n">
         <v>22</v>
@@ -3126,7 +3193,7 @@
         <v>26</v>
       </c>
       <c r="AK15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL15" t="n">
         <v>26</v>
@@ -3135,7 +3202,7 @@
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO15" t="n">
         <v>15</v>
@@ -3144,10 +3211,10 @@
         <v>13</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS15" t="n">
         <v>26</v>
@@ -3162,13 +3229,13 @@
         <v>16</v>
       </c>
       <c r="AW15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX15" t="n">
         <v>26</v>
       </c>
       <c r="AY15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ15" t="n">
         <v>23</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-0.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE16" t="n">
         <v>15</v>
@@ -3302,7 +3369,7 @@
         <v>16</v>
       </c>
       <c r="AI16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ16" t="n">
         <v>13</v>
@@ -3311,7 +3378,7 @@
         <v>20</v>
       </c>
       <c r="AL16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM16" t="n">
         <v>6</v>
@@ -3323,7 +3390,7 @@
         <v>28</v>
       </c>
       <c r="AP16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ16" t="n">
         <v>28</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -3391,43 +3458,43 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E17" t="n">
         <v>11</v>
       </c>
       <c r="F17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>0.423</v>
+        <v>0.407</v>
       </c>
       <c r="H17" t="n">
         <v>48.6</v>
       </c>
       <c r="I17" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="J17" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="K17" t="n">
-        <v>0.435</v>
+        <v>0.436</v>
       </c>
       <c r="L17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="M17" t="n">
         <v>14.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.343</v>
+        <v>0.346</v>
       </c>
       <c r="O17" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="P17" t="n">
-        <v>26</v>
+        <v>25.7</v>
       </c>
       <c r="Q17" t="n">
         <v>0.77</v>
@@ -3436,16 +3503,16 @@
         <v>13.2</v>
       </c>
       <c r="S17" t="n">
-        <v>30.7</v>
+        <v>30.3</v>
       </c>
       <c r="T17" t="n">
-        <v>44</v>
+        <v>43.5</v>
       </c>
       <c r="U17" t="n">
         <v>20.4</v>
       </c>
       <c r="V17" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="W17" t="n">
         <v>6.6</v>
@@ -3457,31 +3524,31 @@
         <v>5.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>96.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>-1.7</v>
+        <v>-2.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG17" t="n">
         <v>20</v>
       </c>
       <c r="AH17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI17" t="n">
         <v>21</v>
@@ -3490,7 +3557,7 @@
         <v>10</v>
       </c>
       <c r="AK17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL17" t="n">
         <v>25</v>
@@ -3499,7 +3566,7 @@
         <v>24</v>
       </c>
       <c r="AN17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO17" t="n">
         <v>8</v>
@@ -3517,13 +3584,13 @@
         <v>14</v>
       </c>
       <c r="AT17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AU17" t="n">
         <v>18</v>
       </c>
       <c r="AV17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AW17" t="n">
         <v>24</v>
@@ -3532,7 +3599,7 @@
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
@@ -3541,10 +3608,10 @@
         <v>5</v>
       </c>
       <c r="BB17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BC17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-7.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE18" t="n">
         <v>28</v>
@@ -3663,7 +3730,7 @@
         <v>29</v>
       </c>
       <c r="AH18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI18" t="n">
         <v>24</v>
@@ -3684,13 +3751,13 @@
         <v>28</v>
       </c>
       <c r="AO18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP18" t="n">
         <v>18</v>
       </c>
-      <c r="AP18" t="n">
-        <v>17</v>
-      </c>
       <c r="AQ18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR18" t="n">
         <v>8</v>
@@ -3702,10 +3769,10 @@
         <v>15</v>
       </c>
       <c r="AU18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AV18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW18" t="n">
         <v>29</v>
@@ -3717,7 +3784,7 @@
         <v>29</v>
       </c>
       <c r="AZ18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA18" t="n">
         <v>19</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-2.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE19" t="n">
         <v>15</v>
@@ -3854,7 +3921,7 @@
         <v>15</v>
       </c>
       <c r="AK19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL19" t="n">
         <v>7</v>
@@ -3863,16 +3930,16 @@
         <v>4</v>
       </c>
       <c r="AN19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AO19" t="n">
         <v>5</v>
       </c>
       <c r="AP19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR19" t="n">
         <v>12</v>
@@ -3884,7 +3951,7 @@
         <v>18</v>
       </c>
       <c r="AU19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV19" t="n">
         <v>6</v>
@@ -3893,7 +3960,7 @@
         <v>27</v>
       </c>
       <c r="AX19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY19" t="n">
         <v>22</v>
@@ -3905,7 +3972,7 @@
         <v>9</v>
       </c>
       <c r="BB19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC19" t="n">
         <v>21</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -4036,7 +4103,7 @@
         <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL20" t="n">
         <v>6</v>
@@ -4078,7 +4145,7 @@
         <v>24</v>
       </c>
       <c r="AY20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ20" t="n">
         <v>16</v>
@@ -4087,10 +4154,10 @@
         <v>15</v>
       </c>
       <c r="BB20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -4197,10 +4264,10 @@
         <v>-2</v>
       </c>
       <c r="AD21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF21" t="n">
         <v>18</v>
@@ -4218,7 +4285,7 @@
         <v>2</v>
       </c>
       <c r="AK21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4227,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO21" t="n">
         <v>27</v>
@@ -4236,7 +4303,7 @@
         <v>28</v>
       </c>
       <c r="AQ21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR21" t="n">
         <v>18</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-9.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
         <v>30</v>
@@ -4409,13 +4476,13 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ22" t="n">
         <v>23</v>
@@ -4433,7 +4500,7 @@
         <v>26</v>
       </c>
       <c r="AV22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW22" t="n">
         <v>14</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F23" t="n">
         <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>0.769</v>
+        <v>0.76</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
@@ -4501,40 +4568,40 @@
         <v>36</v>
       </c>
       <c r="J23" t="n">
-        <v>79</v>
+        <v>78.8</v>
       </c>
       <c r="K23" t="n">
         <v>0.456</v>
       </c>
       <c r="L23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M23" t="n">
         <v>25.1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.365</v>
+        <v>0.37</v>
       </c>
       <c r="O23" t="n">
-        <v>19.2</v>
+        <v>19.6</v>
       </c>
       <c r="P23" t="n">
-        <v>26.7</v>
+        <v>27.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.718</v>
+        <v>0.717</v>
       </c>
       <c r="R23" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S23" t="n">
-        <v>32.1</v>
+        <v>31.8</v>
       </c>
       <c r="T23" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="U23" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="V23" t="n">
         <v>14.5</v>
@@ -4546,25 +4613,25 @@
         <v>6.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.8</v>
+        <v>20.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>22.6</v>
+        <v>23</v>
       </c>
       <c r="AB23" t="n">
-        <v>100.4</v>
+        <v>100.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AE23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF23" t="n">
         <v>4</v>
@@ -4573,16 +4640,16 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AI23" t="n">
         <v>19</v>
       </c>
       <c r="AJ23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AK23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL23" t="n">
         <v>2</v>
@@ -4591,28 +4658,28 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV23" t="n">
         <v>15</v>
@@ -4624,16 +4691,16 @@
         <v>3</v>
       </c>
       <c r="AY23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BA23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB23" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BC23" t="n">
         <v>4</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -4743,10 +4810,10 @@
         <v>-0.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF24" t="n">
         <v>18</v>
@@ -4779,7 +4846,7 @@
         <v>24</v>
       </c>
       <c r="AP24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ24" t="n">
         <v>27</v>
@@ -4788,7 +4855,7 @@
         <v>1</v>
       </c>
       <c r="AS24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT24" t="n">
         <v>4</v>
@@ -4797,7 +4864,7 @@
         <v>25</v>
       </c>
       <c r="AV24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW24" t="n">
         <v>12</v>
@@ -4806,7 +4873,7 @@
         <v>17</v>
       </c>
       <c r="AY24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ24" t="n">
         <v>6</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -4847,100 +4914,100 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E25" t="n">
         <v>15</v>
       </c>
       <c r="F25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G25" t="n">
-        <v>0.577</v>
+        <v>0.6</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="J25" t="n">
-        <v>76.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="K25" t="n">
-        <v>0.501</v>
+        <v>0.498</v>
       </c>
       <c r="L25" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="M25" t="n">
         <v>18</v>
       </c>
       <c r="N25" t="n">
-        <v>0.398</v>
+        <v>0.388</v>
       </c>
       <c r="O25" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="P25" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.748</v>
+        <v>0.743</v>
       </c>
       <c r="R25" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>31</v>
+        <v>31.2</v>
       </c>
       <c r="T25" t="n">
-        <v>40</v>
+        <v>40.4</v>
       </c>
       <c r="U25" t="n">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="V25" t="n">
         <v>16.3</v>
       </c>
       <c r="W25" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="X25" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y25" t="n">
         <v>4.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA25" t="n">
         <v>22</v>
       </c>
       <c r="AB25" t="n">
-        <v>103.2</v>
+        <v>102.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AE25" t="n">
         <v>9</v>
       </c>
       <c r="AF25" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AG25" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AH25" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AI25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ25" t="n">
         <v>27</v>
@@ -4949,49 +5016,49 @@
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AM25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AO25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AP25" t="n">
         <v>8</v>
       </c>
       <c r="AQ25" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AR25" t="n">
         <v>28</v>
       </c>
       <c r="AS25" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AT25" t="n">
         <v>22</v>
       </c>
       <c r="AU25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV25" t="n">
         <v>30</v>
       </c>
       <c r="AW25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY25" t="n">
         <v>8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA25" t="n">
         <v>8</v>
@@ -5000,7 +5067,7 @@
         <v>5</v>
       </c>
       <c r="BC25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -5032,25 +5099,25 @@
         <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G26" t="n">
-        <v>0.654</v>
+        <v>0.615</v>
       </c>
       <c r="H26" t="n">
         <v>48.6</v>
       </c>
       <c r="I26" t="n">
-        <v>37</v>
+        <v>36.4</v>
       </c>
       <c r="J26" t="n">
-        <v>80</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.462</v>
+        <v>0.455</v>
       </c>
       <c r="L26" t="n">
         <v>8</v>
@@ -5059,76 +5126,76 @@
         <v>20.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0.393</v>
+        <v>0.39</v>
       </c>
       <c r="O26" t="n">
-        <v>18.5</v>
+        <v>17.9</v>
       </c>
       <c r="P26" t="n">
-        <v>23.7</v>
+        <v>23.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.781</v>
+        <v>0.777</v>
       </c>
       <c r="R26" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="S26" t="n">
-        <v>28.2</v>
+        <v>28.7</v>
       </c>
       <c r="T26" t="n">
-        <v>41.8</v>
+        <v>42.2</v>
       </c>
       <c r="U26" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V26" t="n">
-        <v>12.8</v>
+        <v>13.1</v>
       </c>
       <c r="W26" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="X26" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>100.5</v>
+        <v>98.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AH26" t="n">
         <v>7</v>
       </c>
       <c r="AI26" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AJ26" t="n">
         <v>16</v>
       </c>
       <c r="AK26" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AL26" t="n">
         <v>5</v>
@@ -5137,52 +5204,52 @@
         <v>7</v>
       </c>
       <c r="AN26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO26" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AP26" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR26" t="n">
         <v>2</v>
       </c>
       <c r="AS26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY26" t="n">
         <v>1</v>
       </c>
       <c r="AZ26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BB26" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BC26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-8.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5301,7 +5368,7 @@
         <v>26</v>
       </c>
       <c r="AH27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI27" t="n">
         <v>10</v>
@@ -5322,10 +5389,10 @@
         <v>30</v>
       </c>
       <c r="AO27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ27" t="n">
         <v>11</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5460,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E28" t="n">
         <v>15</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6</v>
+        <v>0.625</v>
       </c>
       <c r="H28" t="n">
         <v>48.8</v>
       </c>
       <c r="I28" t="n">
-        <v>36.3</v>
+        <v>36.6</v>
       </c>
       <c r="J28" t="n">
-        <v>78.90000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="K28" t="n">
-        <v>0.46</v>
+        <v>0.464</v>
       </c>
       <c r="L28" t="n">
         <v>8.199999999999999</v>
@@ -5426,16 +5493,16 @@
         <v>0.395</v>
       </c>
       <c r="O28" t="n">
-        <v>15.2</v>
+        <v>15.5</v>
       </c>
       <c r="P28" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="Q28" t="n">
         <v>0.756</v>
       </c>
       <c r="R28" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="S28" t="n">
         <v>31.9</v>
@@ -5444,10 +5511,10 @@
         <v>40.8</v>
       </c>
       <c r="U28" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="V28" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="W28" t="n">
         <v>5</v>
@@ -5456,43 +5523,43 @@
         <v>3.8</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>96.09999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AD28" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="AE28" t="n">
         <v>9</v>
       </c>
       <c r="AF28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AH28" t="n">
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AJ28" t="n">
         <v>20</v>
       </c>
       <c r="AK28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
         <v>4</v>
@@ -5501,7 +5568,7 @@
         <v>5</v>
       </c>
       <c r="AN28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO28" t="n">
         <v>30</v>
@@ -5516,7 +5583,7 @@
         <v>29</v>
       </c>
       <c r="AS28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT28" t="n">
         <v>20</v>
@@ -5525,7 +5592,7 @@
         <v>7</v>
       </c>
       <c r="AV28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW28" t="n">
         <v>30</v>
@@ -5537,16 +5604,16 @@
         <v>9</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA28" t="n">
         <v>28</v>
       </c>
       <c r="BB28" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BC28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-4.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE29" t="n">
         <v>21</v>
@@ -5683,13 +5750,13 @@
         <v>19</v>
       </c>
       <c r="AN29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO29" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AP29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5719,13 +5786,13 @@
         <v>16</v>
       </c>
       <c r="AZ29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA29" t="n">
         <v>16</v>
       </c>
       <c r="BB29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC29" t="n">
         <v>24</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -5838,19 +5905,19 @@
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG30" t="n">
         <v>13</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>12</v>
       </c>
       <c r="AH30" t="n">
         <v>24</v>
       </c>
       <c r="AI30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ30" t="n">
         <v>24</v>
@@ -5871,10 +5938,10 @@
         <v>7</v>
       </c>
       <c r="AP30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR30" t="n">
         <v>9</v>
@@ -5907,7 +5974,7 @@
         <v>4</v>
       </c>
       <c r="BB30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC30" t="n">
         <v>9</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-6.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6050,10 +6117,10 @@
         <v>25</v>
       </c>
       <c r="AO31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ31" t="n">
         <v>22</v>
@@ -6062,7 +6129,7 @@
         <v>14</v>
       </c>
       <c r="AS31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT31" t="n">
         <v>24</v>
@@ -6086,7 +6153,7 @@
         <v>15</v>
       </c>
       <c r="BA31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB31" t="n">
         <v>19</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-18-2008-09</t>
+          <t>2008-12-18</t>
         </is>
       </c>
     </row>
